--- a/data.mn/public/datasets/nso-live-births-by-region-monthly.xlsx
+++ b/data.mn/public/datasets/nso-live-births-by-region-monthly.xlsx
@@ -414,32 +414,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W128"/>
+  <dimension ref="A1:W130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="8" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="5" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
     <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9450,7 +9450,7 @@
         <v>40</v>
       </c>
       <c r="S123" t="n">
-        <v>2668</v>
+        <v>2276</v>
       </c>
       <c r="T123" t="n">
         <v>87</v>
@@ -9523,7 +9523,7 @@
         <v>46</v>
       </c>
       <c r="S124" t="n">
-        <v>2119</v>
+        <v>2511</v>
       </c>
       <c r="T124" t="n">
         <v>86</v>
@@ -9828,6 +9828,152 @@
       </c>
       <c r="W128" t="n">
         <v>84</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>80</v>
+      </c>
+      <c r="C129" t="n">
+        <v>171</v>
+      </c>
+      <c r="D129" t="n">
+        <v>93</v>
+      </c>
+      <c r="E129" t="n">
+        <v>33</v>
+      </c>
+      <c r="F129" t="n">
+        <v>133</v>
+      </c>
+      <c r="G129" t="n">
+        <v>101</v>
+      </c>
+      <c r="H129" t="n">
+        <v>57</v>
+      </c>
+      <c r="I129" t="n">
+        <v>37</v>
+      </c>
+      <c r="J129" t="n">
+        <v>66</v>
+      </c>
+      <c r="K129" t="n">
+        <v>25</v>
+      </c>
+      <c r="L129" t="n">
+        <v>82</v>
+      </c>
+      <c r="M129" t="n">
+        <v>109</v>
+      </c>
+      <c r="N129" t="n">
+        <v>121</v>
+      </c>
+      <c r="O129" t="n">
+        <v>163</v>
+      </c>
+      <c r="P129" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>60</v>
+      </c>
+      <c r="R129" t="n">
+        <v>55</v>
+      </c>
+      <c r="S129" t="n">
+        <v>2353</v>
+      </c>
+      <c r="T129" t="n">
+        <v>71</v>
+      </c>
+      <c r="U129" t="n">
+        <v>98</v>
+      </c>
+      <c r="V129" t="n">
+        <v>139</v>
+      </c>
+      <c r="W129" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>82</v>
+      </c>
+      <c r="C130" t="n">
+        <v>194</v>
+      </c>
+      <c r="D130" t="n">
+        <v>91</v>
+      </c>
+      <c r="E130" t="n">
+        <v>41</v>
+      </c>
+      <c r="F130" t="n">
+        <v>144</v>
+      </c>
+      <c r="G130" t="n">
+        <v>95</v>
+      </c>
+      <c r="H130" t="n">
+        <v>71</v>
+      </c>
+      <c r="I130" t="n">
+        <v>42</v>
+      </c>
+      <c r="J130" t="n">
+        <v>58</v>
+      </c>
+      <c r="K130" t="n">
+        <v>22</v>
+      </c>
+      <c r="L130" t="n">
+        <v>63</v>
+      </c>
+      <c r="M130" t="n">
+        <v>136</v>
+      </c>
+      <c r="N130" t="n">
+        <v>170</v>
+      </c>
+      <c r="O130" t="n">
+        <v>154</v>
+      </c>
+      <c r="P130" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>46</v>
+      </c>
+      <c r="R130" t="n">
+        <v>43</v>
+      </c>
+      <c r="S130" t="n">
+        <v>2566</v>
+      </c>
+      <c r="T130" t="n">
+        <v>75</v>
+      </c>
+      <c r="U130" t="n">
+        <v>115</v>
+      </c>
+      <c r="V130" t="n">
+        <v>117</v>
+      </c>
+      <c r="W130" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -9841,32 +9987,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W128"/>
+  <dimension ref="A1:W130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18874,7 +19020,7 @@
         <v>99</v>
       </c>
       <c r="R123" t="n">
-        <v>2668</v>
+        <v>2276</v>
       </c>
       <c r="S123" t="n">
         <v>111</v>
@@ -18947,7 +19093,7 @@
         <v>107</v>
       </c>
       <c r="R124" t="n">
-        <v>2119</v>
+        <v>2511</v>
       </c>
       <c r="S124" t="n">
         <v>121</v>
@@ -19255,6 +19401,152 @@
       </c>
       <c r="W128" t="n">
         <v>89</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>80</v>
+      </c>
+      <c r="C129" t="n">
+        <v>171</v>
+      </c>
+      <c r="D129" t="n">
+        <v>93</v>
+      </c>
+      <c r="E129" t="n">
+        <v>33</v>
+      </c>
+      <c r="F129" t="n">
+        <v>66</v>
+      </c>
+      <c r="G129" t="n">
+        <v>25</v>
+      </c>
+      <c r="H129" t="n">
+        <v>133</v>
+      </c>
+      <c r="I129" t="n">
+        <v>57</v>
+      </c>
+      <c r="J129" t="n">
+        <v>101</v>
+      </c>
+      <c r="K129" t="n">
+        <v>37</v>
+      </c>
+      <c r="L129" t="n">
+        <v>53</v>
+      </c>
+      <c r="M129" t="n">
+        <v>163</v>
+      </c>
+      <c r="N129" t="n">
+        <v>83</v>
+      </c>
+      <c r="O129" t="n">
+        <v>60</v>
+      </c>
+      <c r="P129" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>98</v>
+      </c>
+      <c r="R129" t="n">
+        <v>2353</v>
+      </c>
+      <c r="S129" t="n">
+        <v>109</v>
+      </c>
+      <c r="T129" t="n">
+        <v>82</v>
+      </c>
+      <c r="U129" t="n">
+        <v>121</v>
+      </c>
+      <c r="V129" t="n">
+        <v>139</v>
+      </c>
+      <c r="W129" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>82</v>
+      </c>
+      <c r="C130" t="n">
+        <v>194</v>
+      </c>
+      <c r="D130" t="n">
+        <v>91</v>
+      </c>
+      <c r="E130" t="n">
+        <v>41</v>
+      </c>
+      <c r="F130" t="n">
+        <v>58</v>
+      </c>
+      <c r="G130" t="n">
+        <v>22</v>
+      </c>
+      <c r="H130" t="n">
+        <v>144</v>
+      </c>
+      <c r="I130" t="n">
+        <v>71</v>
+      </c>
+      <c r="J130" t="n">
+        <v>95</v>
+      </c>
+      <c r="K130" t="n">
+        <v>42</v>
+      </c>
+      <c r="L130" t="n">
+        <v>95</v>
+      </c>
+      <c r="M130" t="n">
+        <v>154</v>
+      </c>
+      <c r="N130" t="n">
+        <v>75</v>
+      </c>
+      <c r="O130" t="n">
+        <v>46</v>
+      </c>
+      <c r="P130" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>115</v>
+      </c>
+      <c r="R130" t="n">
+        <v>2566</v>
+      </c>
+      <c r="S130" t="n">
+        <v>136</v>
+      </c>
+      <c r="T130" t="n">
+        <v>63</v>
+      </c>
+      <c r="U130" t="n">
+        <v>170</v>
+      </c>
+      <c r="V130" t="n">
+        <v>117</v>
+      </c>
+      <c r="W130" t="n">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
